--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.78348855063678</v>
+        <v>11.50231688947848</v>
       </c>
       <c r="D2" t="n">
-        <v>48.61990450816443</v>
+        <v>7.900734482576721</v>
       </c>
       <c r="E2" t="n">
-        <v>15.05338090706943</v>
+        <v>2.446174397398782</v>
       </c>
       <c r="F2" t="n">
-        <v>11.43266219188737</v>
+        <v>1.857807606181698</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.51098307680195</v>
+        <v>12.59553474998032</v>
       </c>
       <c r="D3" t="n">
-        <v>60.71983203441114</v>
+        <v>9.866972705591811</v>
       </c>
       <c r="E3" t="n">
-        <v>15.05338090706943</v>
+        <v>2.446174397398782</v>
       </c>
       <c r="F3" t="n">
-        <v>11.43266219188737</v>
+        <v>1.857807606181698</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.15558676574455</v>
+        <v>8.475282849433491</v>
       </c>
       <c r="D4" t="n">
-        <v>27.36068623254424</v>
+        <v>4.446111512788439</v>
       </c>
       <c r="E4" t="n">
-        <v>15.05338090706943</v>
+        <v>2.446174397398782</v>
       </c>
       <c r="F4" t="n">
-        <v>11.43266219188737</v>
+        <v>1.857807606181698</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.10835022317138</v>
+        <v>8.95510691126535</v>
       </c>
       <c r="D5" t="n">
-        <v>38.20013088982812</v>
+        <v>6.207521269597069</v>
       </c>
       <c r="E5" t="n">
-        <v>15.05338090706943</v>
+        <v>2.446174397398782</v>
       </c>
       <c r="F5" t="n">
-        <v>11.43266219188737</v>
+        <v>1.857807606181698</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>71.84634229763154</v>
+        <v>11.67503062336512</v>
       </c>
       <c r="D6" t="n">
-        <v>51.37747020284714</v>
+        <v>8.34883890796266</v>
       </c>
       <c r="E6" t="n">
-        <v>15.05338090706943</v>
+        <v>2.446174397398782</v>
       </c>
       <c r="F6" t="n">
-        <v>11.43266219188737</v>
+        <v>1.857807606181698</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.33541800928104</v>
+        <v>5.41700542650817</v>
       </c>
       <c r="D7" t="n">
-        <v>32.94518510717356</v>
+        <v>5.353592579915703</v>
       </c>
       <c r="E7" t="n">
-        <v>15.05338090706943</v>
+        <v>2.446174397398782</v>
       </c>
       <c r="F7" t="n">
-        <v>11.43266219188737</v>
+        <v>1.857807606181698</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
